--- a/datasets/tenant-inputs/generated/meridian-health/standard-2026-07-v3/core-dimensions/05_data_assets_integrations.xlsx
+++ b/datasets/tenant-inputs/generated/meridian-health/standard-2026-07-v3/core-dimensions/05_data_assets_integrations.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R48398d65ee024ac2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R56b7e085df894bbb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R7c7457b66c514d0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R217cb0133c054c4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="Rbd55d5902a3a4207"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="Re1772b480e684249"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R6d883643ab764794"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R8ca97349e2154dde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="Rcdd35ebcc26d4f57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="Rb38ae6e229b6466c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R3e0160839d2f4667"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R45027b268f984a44"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -628,7 +628,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0cd794d2b28142af"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R21dadca1b2054696"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -809,7 +809,7 @@
         <x:v>Chief Strategy Officer / Executive Office data steward</x:v>
       </x:c>
       <x:c r="O6" s="78" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Executive Office Operational Dataset (record 1) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for data assets integrations.</x:v>
       </x:c>
       <x:c r="P6" s="41" t="str">
         <x:v>Medium</x:v>
@@ -859,7 +859,7 @@
         <x:v>Chief Strategy Officer / Executive Office data steward</x:v>
       </x:c>
       <x:c r="O7" s="79" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm Executive Office Analytics Mart (record 2) current-vs-target status, module boundary, volume baseline, and relationship links before this data assets integrations record is used downstream.</x:v>
       </x:c>
       <x:c r="P7" s="45" t="str">
         <x:v>High</x:v>
@@ -909,7 +909,7 @@
         <x:v>Chief Strategy Officer / Executive Office data steward</x:v>
       </x:c>
       <x:c r="O8" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Attach client evidence for Executive Office Dashboard Inventory (record 3), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P8" t="str">
         <x:v>High</x:v>
@@ -959,7 +959,7 @@
         <x:v>Chief Strategy Officer / Executive Office data steward</x:v>
       </x:c>
       <x:c r="O9" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Reconcile Executive Office Data Quality Rules (record 4) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P9" t="str">
         <x:v>High</x:v>
@@ -1009,7 +1009,7 @@
         <x:v>CMO / Provider Operations data steward</x:v>
       </x:c>
       <x:c r="O10" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Provider Operations Operational Dataset (record 5) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P10" t="str">
         <x:v>Medium</x:v>
@@ -1059,7 +1059,7 @@
         <x:v>CMO / Provider Operations data steward</x:v>
       </x:c>
       <x:c r="O11" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Provider Operations Analytics Mart (record 6) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for data assets integrations.</x:v>
       </x:c>
       <x:c r="P11" t="str">
         <x:v>High</x:v>
@@ -1109,7 +1109,7 @@
         <x:v>CMO / Provider Operations data steward</x:v>
       </x:c>
       <x:c r="O12" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm Provider Operations Dashboard Inventory (record 7) current-vs-target status, module boundary, volume baseline, and relationship links before this data assets integrations record is used downstream.</x:v>
       </x:c>
       <x:c r="P12" t="str">
         <x:v>High</x:v>
@@ -1159,7 +1159,7 @@
         <x:v>CMO / Provider Operations data steward</x:v>
       </x:c>
       <x:c r="O13" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Attach client evidence for Provider Operations Data Quality Rules (record 8), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P13" t="str">
         <x:v>High</x:v>
@@ -1209,7 +1209,7 @@
         <x:v>Health Plan COO / Claims Operations data steward</x:v>
       </x:c>
       <x:c r="O14" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Reconcile Claims Operations Operational Dataset (record 9) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P14" t="str">
         <x:v>Medium</x:v>
@@ -1259,7 +1259,7 @@
         <x:v>Health Plan COO / Claims Operations data steward</x:v>
       </x:c>
       <x:c r="O15" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Claims Operations Analytics Mart (record 10) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P15" t="str">
         <x:v>High</x:v>
@@ -1309,7 +1309,7 @@
         <x:v>Health Plan COO / Claims Operations data steward</x:v>
       </x:c>
       <x:c r="O16" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Claims Operations Dashboard Inventory (record 11) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for data assets integrations.</x:v>
       </x:c>
       <x:c r="P16" t="str">
         <x:v>High</x:v>
@@ -1359,7 +1359,7 @@
         <x:v>Health Plan COO / Claims Operations data steward</x:v>
       </x:c>
       <x:c r="O17" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm Claims Operations Data Quality Rules (record 12) current-vs-target status, module boundary, volume baseline, and relationship links before this data assets integrations record is used downstream.</x:v>
       </x:c>
       <x:c r="P17" t="str">
         <x:v>High</x:v>
@@ -1409,7 +1409,7 @@
         <x:v>VP Benefits Operations / Eligibility and Benefits data steward</x:v>
       </x:c>
       <x:c r="O18" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Attach client evidence for Eligibility Benefits Operational Dataset (record 13), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P18" t="str">
         <x:v>Medium</x:v>
@@ -1459,7 +1459,7 @@
         <x:v>VP Benefits Operations / Eligibility and Benefits data steward</x:v>
       </x:c>
       <x:c r="O19" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Reconcile Eligibility Benefits Analytics Mart (record 14) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P19" t="str">
         <x:v>High</x:v>
@@ -1509,7 +1509,7 @@
         <x:v>VP Benefits Operations / Eligibility and Benefits data steward</x:v>
       </x:c>
       <x:c r="O20" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Eligibility Benefits Dashboard Inventory (record 15) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P20" t="str">
         <x:v>High</x:v>
@@ -1559,7 +1559,7 @@
         <x:v>VP Benefits Operations / Eligibility and Benefits data steward</x:v>
       </x:c>
       <x:c r="O21" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Eligibility Benefits Data Quality Rules (record 16) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for data assets integrations.</x:v>
       </x:c>
       <x:c r="P21" t="str">
         <x:v>High</x:v>
@@ -1609,7 +1609,7 @@
         <x:v>VP Utilization Management / Prior Authorization and UM data steward</x:v>
       </x:c>
       <x:c r="O22" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm Prior Authorization UM Operational Dataset (record 17) current-vs-target status, module boundary, volume baseline, and relationship links before this data assets integrations record is used downstream.</x:v>
       </x:c>
       <x:c r="P22" t="str">
         <x:v>Medium</x:v>
@@ -1659,7 +1659,7 @@
         <x:v>VP Utilization Management / Prior Authorization and UM data steward</x:v>
       </x:c>
       <x:c r="O23" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Attach client evidence for Prior Authorization UM Analytics Mart (record 18), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P23" t="str">
         <x:v>High</x:v>
@@ -1709,7 +1709,7 @@
         <x:v>VP Utilization Management / Prior Authorization and UM data steward</x:v>
       </x:c>
       <x:c r="O24" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Reconcile Prior Authorization UM Dashboard Inventory (record 19) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P24" t="str">
         <x:v>High</x:v>
@@ -1759,7 +1759,7 @@
         <x:v>VP Utilization Management / Prior Authorization and UM data steward</x:v>
       </x:c>
       <x:c r="O25" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Prior Authorization UM Data Quality Rules (record 20) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P25" t="str">
         <x:v>High</x:v>
@@ -1779,7 +1779,7 @@
         <x:v>Operational data asset / interface</x:v>
       </x:c>
       <x:c r="E26" t="str">
-        <x:v>Supports member calls, CRM case management, next-best-action workflows, reporting, downstream analytics, and module context retrieval.</x:v>
+        <x:v>Agent Assist / Member Service data asset used to explain Agents search Salesforce cases, benefits notes, prior-auth status, and claims inquiry screens separately while the member waits on the call.</x:v>
       </x:c>
       <x:c r="F26" t="str">
         <x:v>Genesys Cloud Contact Center; Salesforce Health Cloud CRM; Call Transcript Lake Landing Zone</x:v>
@@ -1794,13 +1794,13 @@
         <x:v>Near-real-time target; SLA requires validation</x:v>
       </x:c>
       <x:c r="J26" t="str">
-        <x:v>25 datasets/interfaces; 100K to multi-million rows/month synthetic scale</x:v>
+        <x:v>After-call work minutes per agent shift plus source row counts to validate.</x:v>
       </x:c>
       <x:c r="K26" t="str">
-        <x:v>Candidate certification needed</x:v>
+        <x:v>Needs cluster-specific certification: stale knowledge article duplicates.</x:v>
       </x:c>
       <x:c r="L26" t="str">
-        <x:v>Partial lineage; catalog ownership and certification status require validation</x:v>
+        <x:v>Lineage must connect Genesys call sample with queue, intent, handle time, transfer flag, and after-call-work fields. + Salesforce Health Cloud case extract with member inquiry categories and resolution dispositions. to the consuming report/workflow.</x:v>
       </x:c>
       <x:c r="M26" t="str">
         <x:v>PHI/PII/financial confidential pattern - synthetic only</x:v>
@@ -1809,7 +1809,7 @@
         <x:v>Chief Experience Officer / Contact Center and Member Service data steward</x:v>
       </x:c>
       <x:c r="O26" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Contact Center Member Service Operational Dataset (record 21) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P26" t="str">
         <x:v>Medium</x:v>
@@ -1829,7 +1829,7 @@
         <x:v>Data product / mart / subject area</x:v>
       </x:c>
       <x:c r="E27" t="str">
-        <x:v>Supports member calls, CRM case management, next-best-action workflows, reporting, downstream analytics, and module context retrieval.</x:v>
+        <x:v>Agent Assist / Member Service data asset used to explain Call transcript intent labels are inconsistent across billing, eligibility, claims status, and prior authorization categories.</x:v>
       </x:c>
       <x:c r="F27" t="str">
         <x:v>Genesys Cloud Contact Center; Salesforce Health Cloud CRM; Call Transcript Lake Landing Zone</x:v>
@@ -1844,13 +1844,13 @@
         <x:v>Daily; SLA requires validation</x:v>
       </x:c>
       <x:c r="J27" t="str">
-        <x:v>40 datasets/interfaces; 175K to multi-million rows/month synthetic scale</x:v>
+        <x:v>Average handle time by intent plus source row counts to validate.</x:v>
       </x:c>
       <x:c r="K27" t="str">
-        <x:v>Source-backed, not yet active-certified</x:v>
+        <x:v>Needs cluster-specific certification: intent taxonomy drift.</x:v>
       </x:c>
       <x:c r="L27" t="str">
-        <x:v>Partial lineage; catalog ownership and certification status require validation</x:v>
+        <x:v>Lineage must connect Genesys call sample with queue, intent, handle time, transfer flag, and after-call-work fields. + Salesforce Health Cloud case extract with member inquiry categories and resolution dispositions. to the consuming report/workflow.</x:v>
       </x:c>
       <x:c r="M27" t="str">
         <x:v>PHI/PII/financial confidential pattern - synthetic only</x:v>
@@ -1859,7 +1859,7 @@
         <x:v>Chief Experience Officer / Contact Center and Member Service data steward</x:v>
       </x:c>
       <x:c r="O27" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Contact Center Member Service Analytics Mart (record 22) against Agent Assist / Member Service evidence: intent taxonomy drift; confirm audited Claude agent-assist answer packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P27" t="str">
         <x:v>High</x:v>
@@ -1879,7 +1879,7 @@
         <x:v>Operational data asset / interface</x:v>
       </x:c>
       <x:c r="E28" t="str">
-        <x:v>Supports member calls, CRM case management, next-best-action workflows, reporting, downstream analytics, and module context retrieval.</x:v>
+        <x:v>Agent Assist / Member Service data asset used to explain Genesys call metadata and Salesforce case outcomes are not reliably joined to claims and benefits context.</x:v>
       </x:c>
       <x:c r="F28" t="str">
         <x:v>Genesys Cloud Contact Center; Salesforce Health Cloud CRM; Call Transcript Lake Landing Zone</x:v>
@@ -1894,13 +1894,13 @@
         <x:v>Near-real-time target; SLA requires validation</x:v>
       </x:c>
       <x:c r="J28" t="str">
-        <x:v>55 datasets/interfaces; 250K to multi-million rows/month synthetic scale</x:v>
+        <x:v>First contact resolution for claims-status calls plus source row counts to validate.</x:v>
       </x:c>
       <x:c r="K28" t="str">
-        <x:v>Source-backed, not yet active-certified</x:v>
+        <x:v>Needs cluster-specific certification: CRM-to-claims join gaps.</x:v>
       </x:c>
       <x:c r="L28" t="str">
-        <x:v>Partial lineage; catalog ownership and certification status require validation</x:v>
+        <x:v>Lineage must connect Genesys call sample with queue, intent, handle time, transfer flag, and after-call-work fields. + Salesforce Health Cloud case extract with member inquiry categories and resolution dispositions. to the consuming report/workflow.</x:v>
       </x:c>
       <x:c r="M28" t="str">
         <x:v>PHI/PII/financial confidential pattern - synthetic only</x:v>
@@ -1909,7 +1909,7 @@
         <x:v>Chief Experience Officer / Contact Center and Member Service data steward</x:v>
       </x:c>
       <x:c r="O28" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Contact Center Member Service Dashboard Inventory (record 23) against Agent Assist / Member Service evidence: CRM-to-claims join gaps; confirm Genesys-Salesforce-claims context join owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P28" t="str">
         <x:v>High</x:v>
@@ -1929,7 +1929,7 @@
         <x:v>Operational data asset / interface</x:v>
       </x:c>
       <x:c r="E29" t="str">
-        <x:v>Supports member calls, CRM case management, next-best-action workflows, reporting, downstream analytics, and module context retrieval.</x:v>
+        <x:v>Agent Assist / Member Service data asset used to explain Knowledge articles are duplicated across operations playbooks and CRM snippets, creating conflicting guidance for appeal and denial inquiries.</x:v>
       </x:c>
       <x:c r="F29" t="str">
         <x:v>Genesys Cloud Contact Center; Salesforce Health Cloud CRM; Call Transcript Lake Landing Zone</x:v>
@@ -1944,13 +1944,13 @@
         <x:v>Daily; SLA requires validation</x:v>
       </x:c>
       <x:c r="J29" t="str">
-        <x:v>70 datasets/interfaces; 325K to multi-million rows/month synthetic scale</x:v>
+        <x:v>After-call work minutes per agent shift plus source row counts to validate.</x:v>
       </x:c>
       <x:c r="K29" t="str">
-        <x:v>Candidate certification needed</x:v>
+        <x:v>Needs cluster-specific certification: stale knowledge article duplicates.</x:v>
       </x:c>
       <x:c r="L29" t="str">
-        <x:v>Partial lineage; catalog ownership and certification status require validation</x:v>
+        <x:v>Lineage must connect Genesys call sample with queue, intent, handle time, transfer flag, and after-call-work fields. + Salesforce Health Cloud case extract with member inquiry categories and resolution dispositions. to the consuming report/workflow.</x:v>
       </x:c>
       <x:c r="M29" t="str">
         <x:v>PHI/PII/financial confidential pattern - synthetic only</x:v>
@@ -1959,7 +1959,7 @@
         <x:v>Chief Experience Officer / Contact Center and Member Service data steward</x:v>
       </x:c>
       <x:c r="O29" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Contact Center Member Service Data Quality Rules (record 24) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P29" t="str">
         <x:v>High</x:v>
@@ -2009,7 +2009,7 @@
         <x:v>Revenue Cycle Leader / Revenue Cycle Operations data steward</x:v>
       </x:c>
       <x:c r="O30" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Revenue Cycle Operations Operational Dataset (record 25) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P30" t="str">
         <x:v>Medium</x:v>
@@ -2059,7 +2059,7 @@
         <x:v>Revenue Cycle Leader / Revenue Cycle Operations data steward</x:v>
       </x:c>
       <x:c r="O31" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Revenue Cycle Operations Analytics Mart (record 26) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for data assets integrations.</x:v>
       </x:c>
       <x:c r="P31" t="str">
         <x:v>High</x:v>
@@ -2109,7 +2109,7 @@
         <x:v>Revenue Cycle Leader / Revenue Cycle Operations data steward</x:v>
       </x:c>
       <x:c r="O32" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm Revenue Cycle Operations Dashboard Inventory (record 27) current-vs-target status, module boundary, volume baseline, and relationship links before this data assets integrations record is used downstream.</x:v>
       </x:c>
       <x:c r="P32" t="str">
         <x:v>High</x:v>
@@ -2159,7 +2159,7 @@
         <x:v>Revenue Cycle Leader / Revenue Cycle Operations data steward</x:v>
       </x:c>
       <x:c r="O33" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Attach client evidence for Revenue Cycle Operations Data Quality Rules (record 28), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P33" t="str">
         <x:v>High</x:v>
@@ -2179,7 +2179,7 @@
         <x:v>Data product / mart / subject area</x:v>
       </x:c>
       <x:c r="E34" t="str">
-        <x:v>Supports finance analytics across GL/AP/AR/budget/vendor spend reporting, close reconciliation, and FP&amp;A decision support.</x:v>
+        <x:v>Finance Analytics data asset used to explain Informatica job failures are resolved manually because the finance mart lacks clear lineage from Oracle ERP subledger jobs to report-level consumers.</x:v>
       </x:c>
       <x:c r="F34" t="str">
         <x:v>Oracle ERP Finance; SQL Server Finance Mart; Netezza Finance Subject Area</x:v>
@@ -2194,13 +2194,13 @@
         <x:v>Nightly refresh; month-end close spike; target near-real-time certification TBD</x:v>
       </x:c>
       <x:c r="J34" t="str">
-        <x:v>500 tables; 200 ETL jobs; 1,000 finance reports; 800 BI users where applicable</x:v>
+        <x:v>Certified finance dashboard adoption plus source row counts to validate.</x:v>
       </x:c>
       <x:c r="K34" t="str">
-        <x:v>Candidate certification needed</x:v>
+        <x:v>Needs cluster-specific certification: slow close-window dashboards.</x:v>
       </x:c>
       <x:c r="L34" t="str">
-        <x:v>Incomplete lineage; duplicate reports; target catalog certification via Collibra/Purview</x:v>
+        <x:v>Lineage must connect Oracle ERP Finance GL/AP/AR extract as of 2026-06 synthetic close cycle. + SQL Server Finance Mart schema inventory showing GL, AP, AR, budget, vendor spend, and cost-center schemas. to the consuming report/workflow.</x:v>
       </x:c>
       <x:c r="M34" t="str">
         <x:v>PHI/PII/financial confidential pattern - synthetic only</x:v>
@@ -2209,7 +2209,7 @@
         <x:v>CFO / Finance Analytics data steward</x:v>
       </x:c>
       <x:c r="O34" t="str">
-        <x:v>Validate duplicate reports, slow dashboards, manual reconciliations, vendor spend definitions, and close-window refresh delay.</x:v>
+        <x:v>Validate Finance Mart GL AP AR Subject Area (record 29) against Finance Analytics evidence: slow close-window dashboards; confirm vendor master harmonization owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P34" t="str">
         <x:v>Medium</x:v>
@@ -2229,7 +2229,7 @@
         <x:v>Operational data asset / interface</x:v>
       </x:c>
       <x:c r="E35" t="str">
-        <x:v>Supports finance analytics across GL/AP/AR/budget/vendor spend reporting, close reconciliation, and FP&amp;A decision support.</x:v>
+        <x:v>Finance Analytics data asset used to explain Databricks Finance Gold is the target path, but cost-center hierarchy, vendor master harmonization, and audit signoff are unresolved.</x:v>
       </x:c>
       <x:c r="F35" t="str">
         <x:v>Oracle ERP Finance; SQL Server Finance Mart; Netezza Finance Subject Area</x:v>
@@ -2244,13 +2244,13 @@
         <x:v>Nightly refresh; month-end close spike; target near-real-time certification TBD</x:v>
       </x:c>
       <x:c r="J35" t="str">
-        <x:v>500 tables; 200 ETL jobs; 1,000 finance reports; 800 BI users where applicable</x:v>
+        <x:v>Manual reconciliation hours per close cycle plus source row counts to validate.</x:v>
       </x:c>
       <x:c r="K35" t="str">
-        <x:v>Source-backed, not yet active-certified</x:v>
+        <x:v>Needs cluster-specific certification: incomplete lineage from ERP to BI.</x:v>
       </x:c>
       <x:c r="L35" t="str">
-        <x:v>Incomplete lineage; duplicate reports; target catalog certification via Collibra/Purview</x:v>
+        <x:v>Lineage must connect Oracle ERP Finance GL/AP/AR extract as of 2026-06 synthetic close cycle. + SQL Server Finance Mart schema inventory showing GL, AP, AR, budget, vendor spend, and cost-center schemas. to the consuming report/workflow.</x:v>
       </x:c>
       <x:c r="M35" t="str">
         <x:v>PHI/PII/financial confidential pattern - synthetic only</x:v>
@@ -2259,7 +2259,7 @@
         <x:v>CFO / Finance Analytics data steward</x:v>
       </x:c>
       <x:c r="O35" t="str">
-        <x:v>Validate duplicate reports, slow dashboards, manual reconciliations, vendor spend definitions, and close-window refresh delay.</x:v>
+        <x:v>Validate Vendor Spend and Contract Analytics Dataset (record 30) against Finance Analytics evidence: incomplete lineage from ERP to BI; confirm cost-center hierarchy stewardship owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P35" t="str">
         <x:v>High</x:v>
@@ -2279,7 +2279,7 @@
         <x:v>Operational data asset / interface</x:v>
       </x:c>
       <x:c r="E36" t="str">
-        <x:v>Supports finance analytics across GL/AP/AR/budget/vendor spend reporting, close reconciliation, and FP&amp;A decision support.</x:v>
+        <x:v>Finance Analytics data asset used to explain Month-end close dashboards slow down because 38 priority reports refresh from five SQL Server finance schemas during the same overnight load window.</x:v>
       </x:c>
       <x:c r="F36" t="str">
         <x:v>Oracle ERP Finance; SQL Server Finance Mart; Netezza Finance Subject Area</x:v>
@@ -2294,13 +2294,13 @@
         <x:v>Nightly refresh; month-end close spike; target near-real-time certification TBD</x:v>
       </x:c>
       <x:c r="J36" t="str">
-        <x:v>500 tables; 200 ETL jobs; 1,000 finance reports; 800 BI users where applicable</x:v>
+        <x:v>Close report refresh completion by 6:00 AM CT plus source row counts to validate.</x:v>
       </x:c>
       <x:c r="K36" t="str">
-        <x:v>Source-backed, not yet active-certified</x:v>
+        <x:v>Needs cluster-specific certification: inconsistent vendor spend definitions.</x:v>
       </x:c>
       <x:c r="L36" t="str">
-        <x:v>Incomplete lineage; duplicate reports; target catalog certification via Collibra/Purview</x:v>
+        <x:v>Lineage must connect Oracle ERP Finance GL/AP/AR extract as of 2026-06 synthetic close cycle. + SQL Server Finance Mart schema inventory showing GL, AP, AR, budget, vendor spend, and cost-center schemas. to the consuming report/workflow.</x:v>
       </x:c>
       <x:c r="M36" t="str">
         <x:v>PHI/PII/financial confidential pattern - synthetic only</x:v>
@@ -2309,7 +2309,7 @@
         <x:v>CFO / Finance Analytics data steward</x:v>
       </x:c>
       <x:c r="O36" t="str">
-        <x:v>Validate duplicate reports, slow dashboards, manual reconciliations, vendor spend definitions, and close-window refresh delay.</x:v>
+        <x:v>Validate Month-End Close Reconciliation Workbook (record 31) against Finance Analytics evidence: inconsistent vendor spend definitions; confirm Databricks Finance Gold certification owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P36" t="str">
         <x:v>High</x:v>
@@ -2329,7 +2329,7 @@
         <x:v>Data product / mart / subject area</x:v>
       </x:c>
       <x:c r="E37" t="str">
-        <x:v>Supports finance analytics across GL/AP/AR/budget/vendor spend reporting, close reconciliation, and FP&amp;A decision support.</x:v>
+        <x:v>Finance Analytics data asset used to explain Vendor spend differs across AP, procurement, and contract repository extracts, so sourcing questions need a reconciled vendor-master rule before Source uses the data.</x:v>
       </x:c>
       <x:c r="F37" t="str">
         <x:v>Oracle ERP Finance; SQL Server Finance Mart; Netezza Finance Subject Area</x:v>
@@ -2344,13 +2344,13 @@
         <x:v>Nightly refresh; month-end close spike; target near-real-time certification TBD</x:v>
       </x:c>
       <x:c r="J37" t="str">
-        <x:v>500 tables; 200 ETL jobs; 1,000 finance reports; 800 BI users where applicable</x:v>
+        <x:v>Certified finance dashboard adoption plus source row counts to validate.</x:v>
       </x:c>
       <x:c r="K37" t="str">
-        <x:v>Candidate certification needed</x:v>
+        <x:v>Needs cluster-specific certification: slow close-window dashboards.</x:v>
       </x:c>
       <x:c r="L37" t="str">
-        <x:v>Incomplete lineage; duplicate reports; target catalog certification via Collibra/Purview</x:v>
+        <x:v>Lineage must connect Oracle ERP Finance GL/AP/AR extract as of 2026-06 synthetic close cycle. + SQL Server Finance Mart schema inventory showing GL, AP, AR, budget, vendor spend, and cost-center schemas. to the consuming report/workflow.</x:v>
       </x:c>
       <x:c r="M37" t="str">
         <x:v>PHI/PII/financial confidential pattern - synthetic only</x:v>
@@ -2359,7 +2359,7 @@
         <x:v>CFO / Finance Analytics data steward</x:v>
       </x:c>
       <x:c r="O37" t="str">
-        <x:v>Validate duplicate reports, slow dashboards, manual reconciliations, vendor spend definitions, and close-window refresh delay.</x:v>
+        <x:v>Validate Databricks Finance Gold Data Product (record 32) against Finance Analytics evidence: slow close-window dashboards; confirm vendor master harmonization owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P37" t="str">
         <x:v>High</x:v>
@@ -2409,7 +2409,7 @@
         <x:v>CHRO / Workforce Analytics data steward</x:v>
       </x:c>
       <x:c r="O38" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Attach client evidence for Workforce Analytics Operational Dataset (record 33), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P38" t="str">
         <x:v>Medium</x:v>
@@ -2459,7 +2459,7 @@
         <x:v>CHRO / Workforce Analytics data steward</x:v>
       </x:c>
       <x:c r="O39" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Reconcile Workforce Analytics Analytics Mart (record 34) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P39" t="str">
         <x:v>High</x:v>
@@ -2509,7 +2509,7 @@
         <x:v>CHRO / Workforce Analytics data steward</x:v>
       </x:c>
       <x:c r="O40" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Workforce Analytics Dashboard Inventory (record 35) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P40" t="str">
         <x:v>High</x:v>
@@ -2559,7 +2559,7 @@
         <x:v>CHRO / Workforce Analytics data steward</x:v>
       </x:c>
       <x:c r="O41" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Workforce Analytics Data Quality Rules (record 36) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for data assets integrations.</x:v>
       </x:c>
       <x:c r="P41" t="str">
         <x:v>High</x:v>
@@ -2609,7 +2609,7 @@
         <x:v>VP Quality / Clinical Quality Analytics data steward</x:v>
       </x:c>
       <x:c r="O42" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm Clinical Quality Analytics Operational Dataset (record 37) current-vs-target status, module boundary, volume baseline, and relationship links before this data assets integrations record is used downstream.</x:v>
       </x:c>
       <x:c r="P42" t="str">
         <x:v>Medium</x:v>
@@ -2659,7 +2659,7 @@
         <x:v>VP Quality / Clinical Quality Analytics data steward</x:v>
       </x:c>
       <x:c r="O43" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Attach client evidence for Clinical Quality Analytics Analytics Mart (record 38), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P43" t="str">
         <x:v>High</x:v>
@@ -2709,7 +2709,7 @@
         <x:v>VP Quality / Clinical Quality Analytics data steward</x:v>
       </x:c>
       <x:c r="O44" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Reconcile Clinical Quality Analytics Dashboard Inventory (record 39) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P44" t="str">
         <x:v>High</x:v>
@@ -2759,7 +2759,7 @@
         <x:v>VP Quality / Clinical Quality Analytics data steward</x:v>
       </x:c>
       <x:c r="O45" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Clinical Quality Analytics Data Quality Rules (record 40) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P45" t="str">
         <x:v>High</x:v>
@@ -2809,7 +2809,7 @@
         <x:v>VP Claims Analytics / Claims and Payment Analytics data steward</x:v>
       </x:c>
       <x:c r="O46" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Claims Payment Analytics Operational Dataset (record 41) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for data assets integrations.</x:v>
       </x:c>
       <x:c r="P46" t="str">
         <x:v>Medium</x:v>
@@ -2859,7 +2859,7 @@
         <x:v>VP Claims Analytics / Claims and Payment Analytics data steward</x:v>
       </x:c>
       <x:c r="O47" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm Claims Payment Analytics Analytics Mart (record 42) current-vs-target status, module boundary, volume baseline, and relationship links before this data assets integrations record is used downstream.</x:v>
       </x:c>
       <x:c r="P47" t="str">
         <x:v>High</x:v>
@@ -2909,7 +2909,7 @@
         <x:v>VP Claims Analytics / Claims and Payment Analytics data steward</x:v>
       </x:c>
       <x:c r="O48" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Attach client evidence for Claims Payment Analytics Dashboard Inventory (record 43), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P48" t="str">
         <x:v>High</x:v>
@@ -2959,7 +2959,7 @@
         <x:v>VP Claims Analytics / Claims and Payment Analytics data steward</x:v>
       </x:c>
       <x:c r="O49" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Reconcile Claims Payment Analytics Data Quality Rules (record 44) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P49" t="str">
         <x:v>High</x:v>
@@ -3009,7 +3009,7 @@
         <x:v>VP Provider Performance / Provider Performance Analytics data steward</x:v>
       </x:c>
       <x:c r="O50" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Provider Performance Analytics Operational Dataset (record 45) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P50" t="str">
         <x:v>Medium</x:v>
@@ -3059,7 +3059,7 @@
         <x:v>VP Provider Performance / Provider Performance Analytics data steward</x:v>
       </x:c>
       <x:c r="O51" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Provider Performance Analytics Analytics Mart (record 46) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for data assets integrations.</x:v>
       </x:c>
       <x:c r="P51" t="str">
         <x:v>High</x:v>
@@ -3109,7 +3109,7 @@
         <x:v>VP Provider Performance / Provider Performance Analytics data steward</x:v>
       </x:c>
       <x:c r="O52" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm Provider Performance Analytics Dashboard Inventory (record 47) current-vs-target status, module boundary, volume baseline, and relationship links before this data assets integrations record is used downstream.</x:v>
       </x:c>
       <x:c r="P52" t="str">
         <x:v>High</x:v>
@@ -3159,7 +3159,7 @@
         <x:v>VP Provider Performance / Provider Performance Analytics data steward</x:v>
       </x:c>
       <x:c r="O53" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Attach client evidence for Provider Performance Analytics Data Quality Rules (record 48), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P53" t="str">
         <x:v>High</x:v>
@@ -3209,7 +3209,7 @@
         <x:v>CDAO / Enterprise Data Platform data steward</x:v>
       </x:c>
       <x:c r="O54" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Reconcile Enterprise Data Platform Operational Dataset (record 49) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P54" t="str">
         <x:v>Medium</x:v>
@@ -3259,7 +3259,7 @@
         <x:v>CDAO / Enterprise Data Platform data steward</x:v>
       </x:c>
       <x:c r="O55" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Enterprise Data Platform Analytics Mart (record 50) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P55" t="str">
         <x:v>High</x:v>
@@ -3309,7 +3309,7 @@
         <x:v>CDAO / Enterprise Data Platform data steward</x:v>
       </x:c>
       <x:c r="O56" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Enterprise Data Platform Dashboard Inventory (record 51) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for data assets integrations.</x:v>
       </x:c>
       <x:c r="P56" t="str">
         <x:v>High</x:v>
@@ -3359,7 +3359,7 @@
         <x:v>CDAO / Enterprise Data Platform data steward</x:v>
       </x:c>
       <x:c r="O57" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm Enterprise Data Platform Data Quality Rules (record 52) current-vs-target status, module boundary, volume baseline, and relationship links before this data assets integrations record is used downstream.</x:v>
       </x:c>
       <x:c r="P57" t="str">
         <x:v>High</x:v>
@@ -3409,7 +3409,7 @@
         <x:v>Chief Data Officer / Data Governance and Data Quality data steward</x:v>
       </x:c>
       <x:c r="O58" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Attach client evidence for Data Governance Data Quality Operational Dataset (record 53), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P58" t="str">
         <x:v>Medium</x:v>
@@ -3459,7 +3459,7 @@
         <x:v>Chief Data Officer / Data Governance and Data Quality data steward</x:v>
       </x:c>
       <x:c r="O59" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Reconcile Data Governance Data Quality Analytics Mart (record 54) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P59" t="str">
         <x:v>High</x:v>
@@ -3509,7 +3509,7 @@
         <x:v>Chief Data Officer / Data Governance and Data Quality data steward</x:v>
       </x:c>
       <x:c r="O60" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Data Governance Data Quality Dashboard Inventory (record 55) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P60" t="str">
         <x:v>High</x:v>
@@ -3559,7 +3559,7 @@
         <x:v>Chief Data Officer / Data Governance and Data Quality data steward</x:v>
       </x:c>
       <x:c r="O61" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Data Governance Data Quality Data Quality Rules (record 56) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for data assets integrations.</x:v>
       </x:c>
       <x:c r="P61" t="str">
         <x:v>High</x:v>
@@ -3579,7 +3579,7 @@
         <x:v>Operational data asset / interface</x:v>
       </x:c>
       <x:c r="E62" t="str">
-        <x:v>Supports agent assist, call summarization, intent detection, guided resolution, reporting, downstream analytics, and module context retrieval.</x:v>
+        <x:v>Agent Assist / Member Service data asset used to explain Call transcript intent labels are inconsistent across billing, eligibility, claims status, and prior authorization categories.</x:v>
       </x:c>
       <x:c r="F62" t="str">
         <x:v>Agent Assist and Next Best Action Workflow Platform; Agent Assist and Next Best Action Analytics Mart; Agent Assist and Next Best Action Reporting Workspace</x:v>
@@ -3594,13 +3594,13 @@
         <x:v>Near-real-time target; SLA requires validation</x:v>
       </x:c>
       <x:c r="J62" t="str">
-        <x:v>25 datasets/interfaces; 100K to multi-million rows/month synthetic scale</x:v>
+        <x:v>After-call work minutes per agent shift plus source row counts to validate.</x:v>
       </x:c>
       <x:c r="K62" t="str">
-        <x:v>Candidate certification needed</x:v>
+        <x:v>Needs cluster-specific certification: stale knowledge article duplicates.</x:v>
       </x:c>
       <x:c r="L62" t="str">
-        <x:v>Partial lineage; catalog ownership and certification status require validation</x:v>
+        <x:v>Lineage must connect Genesys call sample with queue, intent, handle time, transfer flag, and after-call-work fields. + Salesforce Health Cloud case extract with member inquiry categories and resolution dispositions. to the consuming report/workflow.</x:v>
       </x:c>
       <x:c r="M62" t="str">
         <x:v>PHI/PII/financial confidential pattern - synthetic only</x:v>
@@ -3609,7 +3609,7 @@
         <x:v>VP Contact Center / Agent Assist and Next Best Action data steward</x:v>
       </x:c>
       <x:c r="O62" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Agent Assist Next Best Action Operational Dataset (record 57) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P62" t="str">
         <x:v>Medium</x:v>
@@ -3629,7 +3629,7 @@
         <x:v>Data product / mart / subject area</x:v>
       </x:c>
       <x:c r="E63" t="str">
-        <x:v>Supports agent assist, call summarization, intent detection, guided resolution, reporting, downstream analytics, and module context retrieval.</x:v>
+        <x:v>Agent Assist / Member Service data asset used to explain Genesys call metadata and Salesforce case outcomes are not reliably joined to claims and benefits context.</x:v>
       </x:c>
       <x:c r="F63" t="str">
         <x:v>Agent Assist and Next Best Action Workflow Platform; Agent Assist and Next Best Action Analytics Mart; Agent Assist and Next Best Action Reporting Workspace</x:v>
@@ -3644,13 +3644,13 @@
         <x:v>Daily; SLA requires validation</x:v>
       </x:c>
       <x:c r="J63" t="str">
-        <x:v>40 datasets/interfaces; 175K to multi-million rows/month synthetic scale</x:v>
+        <x:v>Average handle time by intent plus source row counts to validate.</x:v>
       </x:c>
       <x:c r="K63" t="str">
-        <x:v>Source-backed, not yet active-certified</x:v>
+        <x:v>Needs cluster-specific certification: intent taxonomy drift.</x:v>
       </x:c>
       <x:c r="L63" t="str">
-        <x:v>Partial lineage; catalog ownership and certification status require validation</x:v>
+        <x:v>Lineage must connect Genesys call sample with queue, intent, handle time, transfer flag, and after-call-work fields. + Salesforce Health Cloud case extract with member inquiry categories and resolution dispositions. to the consuming report/workflow.</x:v>
       </x:c>
       <x:c r="M63" t="str">
         <x:v>PHI/PII/financial confidential pattern - synthetic only</x:v>
@@ -3659,7 +3659,7 @@
         <x:v>VP Contact Center / Agent Assist and Next Best Action data steward</x:v>
       </x:c>
       <x:c r="O63" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Agent Assist Next Best Action Analytics Mart (record 58) against Agent Assist / Member Service evidence: intent taxonomy drift; confirm audited Claude agent-assist answer packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P63" t="str">
         <x:v>High</x:v>
@@ -3679,7 +3679,7 @@
         <x:v>Operational data asset / interface</x:v>
       </x:c>
       <x:c r="E64" t="str">
-        <x:v>Supports agent assist, call summarization, intent detection, guided resolution, reporting, downstream analytics, and module context retrieval.</x:v>
+        <x:v>Agent Assist / Member Service data asset used to explain Knowledge articles are duplicated across operations playbooks and CRM snippets, creating conflicting guidance for appeal and denial inquiries.</x:v>
       </x:c>
       <x:c r="F64" t="str">
         <x:v>Agent Assist and Next Best Action Workflow Platform; Agent Assist and Next Best Action Analytics Mart; Agent Assist and Next Best Action Reporting Workspace</x:v>
@@ -3694,13 +3694,13 @@
         <x:v>Near-real-time target; SLA requires validation</x:v>
       </x:c>
       <x:c r="J64" t="str">
-        <x:v>55 datasets/interfaces; 250K to multi-million rows/month synthetic scale</x:v>
+        <x:v>First contact resolution for claims-status calls plus source row counts to validate.</x:v>
       </x:c>
       <x:c r="K64" t="str">
-        <x:v>Source-backed, not yet active-certified</x:v>
+        <x:v>Needs cluster-specific certification: CRM-to-claims join gaps.</x:v>
       </x:c>
       <x:c r="L64" t="str">
-        <x:v>Partial lineage; catalog ownership and certification status require validation</x:v>
+        <x:v>Lineage must connect Genesys call sample with queue, intent, handle time, transfer flag, and after-call-work fields. + Salesforce Health Cloud case extract with member inquiry categories and resolution dispositions. to the consuming report/workflow.</x:v>
       </x:c>
       <x:c r="M64" t="str">
         <x:v>PHI/PII/financial confidential pattern - synthetic only</x:v>
@@ -3709,7 +3709,7 @@
         <x:v>VP Contact Center / Agent Assist and Next Best Action data steward</x:v>
       </x:c>
       <x:c r="O64" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Agent Assist Next Best Action Dashboard Inventory (record 59) against Agent Assist / Member Service evidence: CRM-to-claims join gaps; confirm Genesys-Salesforce-claims context join owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P64" t="str">
         <x:v>High</x:v>
@@ -3729,7 +3729,7 @@
         <x:v>Operational data asset / interface</x:v>
       </x:c>
       <x:c r="E65" t="str">
-        <x:v>Supports agent assist, call summarization, intent detection, guided resolution, reporting, downstream analytics, and module context retrieval.</x:v>
+        <x:v>Agent Assist / Member Service data asset used to explain Supervisors cannot prove whether AI suggestions reduce handle time without a baseline for after-call work, transfer rate, and first-contact resolution.</x:v>
       </x:c>
       <x:c r="F65" t="str">
         <x:v>Agent Assist and Next Best Action Workflow Platform; Agent Assist and Next Best Action Analytics Mart; Agent Assist and Next Best Action Reporting Workspace</x:v>
@@ -3744,13 +3744,13 @@
         <x:v>Daily; SLA requires validation</x:v>
       </x:c>
       <x:c r="J65" t="str">
-        <x:v>70 datasets/interfaces; 325K to multi-million rows/month synthetic scale</x:v>
+        <x:v>After-call work minutes per agent shift plus source row counts to validate.</x:v>
       </x:c>
       <x:c r="K65" t="str">
-        <x:v>Candidate certification needed</x:v>
+        <x:v>Needs cluster-specific certification: stale knowledge article duplicates.</x:v>
       </x:c>
       <x:c r="L65" t="str">
-        <x:v>Partial lineage; catalog ownership and certification status require validation</x:v>
+        <x:v>Lineage must connect Genesys call sample with queue, intent, handle time, transfer flag, and after-call-work fields. + Salesforce Health Cloud case extract with member inquiry categories and resolution dispositions. to the consuming report/workflow.</x:v>
       </x:c>
       <x:c r="M65" t="str">
         <x:v>PHI/PII/financial confidential pattern - synthetic only</x:v>
@@ -3759,7 +3759,7 @@
         <x:v>VP Contact Center / Agent Assist and Next Best Action data steward</x:v>
       </x:c>
       <x:c r="O65" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Agent Assist Next Best Action Data Quality Rules (record 60) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P65" t="str">
         <x:v>High</x:v>
@@ -3809,7 +3809,7 @@
         <x:v>CDAO / Unified Clinical and Claims Lakehouse data steward</x:v>
       </x:c>
       <x:c r="O66" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Unified Clinical Claims Lakehouse Operational Dataset (record 61) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for data assets integrations.</x:v>
       </x:c>
       <x:c r="P66" t="str">
         <x:v>Medium</x:v>
@@ -3859,7 +3859,7 @@
         <x:v>CDAO / Unified Clinical and Claims Lakehouse data steward</x:v>
       </x:c>
       <x:c r="O67" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm Unified Clinical Claims Lakehouse Analytics Mart (record 62) current-vs-target status, module boundary, volume baseline, and relationship links before this data assets integrations record is used downstream.</x:v>
       </x:c>
       <x:c r="P67" t="str">
         <x:v>High</x:v>
@@ -3909,7 +3909,7 @@
         <x:v>CDAO / Unified Clinical and Claims Lakehouse data steward</x:v>
       </x:c>
       <x:c r="O68" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Attach client evidence for Unified Clinical Claims Lakehouse Dashboard Inventory (record 63), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P68" t="str">
         <x:v>High</x:v>
@@ -3959,7 +3959,7 @@
         <x:v>CDAO / Unified Clinical and Claims Lakehouse data steward</x:v>
       </x:c>
       <x:c r="O69" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Reconcile Unified Clinical Claims Lakehouse Data Quality Rules (record 64) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P69" t="str">
         <x:v>High</x:v>
@@ -4009,7 +4009,7 @@
         <x:v>CIO / CFO / IT Budget and Tower Baseline data steward</x:v>
       </x:c>
       <x:c r="O70" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for IT Budget Tower Baseline Operational Dataset (record 65) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P70" t="str">
         <x:v>Medium</x:v>
@@ -4059,7 +4059,7 @@
         <x:v>CIO / CFO / IT Budget and Tower Baseline data steward</x:v>
       </x:c>
       <x:c r="O71" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate IT Budget Tower Baseline Analytics Mart (record 66) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for data assets integrations.</x:v>
       </x:c>
       <x:c r="P71" t="str">
         <x:v>High</x:v>
@@ -4109,7 +4109,7 @@
         <x:v>CIO / CFO / IT Budget and Tower Baseline data steward</x:v>
       </x:c>
       <x:c r="O72" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm IT Budget Tower Baseline Dashboard Inventory (record 67) current-vs-target status, module boundary, volume baseline, and relationship links before this data assets integrations record is used downstream.</x:v>
       </x:c>
       <x:c r="P72" t="str">
         <x:v>High</x:v>
@@ -4159,7 +4159,7 @@
         <x:v>CIO / CFO / IT Budget and Tower Baseline data steward</x:v>
       </x:c>
       <x:c r="O73" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Attach client evidence for IT Budget Tower Baseline Data Quality Rules (record 68), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P73" t="str">
         <x:v>High</x:v>
@@ -4209,7 +4209,7 @@
         <x:v>Chief Procurement Officer / Vendor and Contract Optimization data steward</x:v>
       </x:c>
       <x:c r="O74" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Reconcile Vendor Contract Optimization Operational Dataset (record 69) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P74" t="str">
         <x:v>Medium</x:v>
@@ -4259,7 +4259,7 @@
         <x:v>Chief Procurement Officer / Vendor and Contract Optimization data steward</x:v>
       </x:c>
       <x:c r="O75" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Vendor Contract Optimization Analytics Mart (record 70) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P75" t="str">
         <x:v>High</x:v>
@@ -4309,7 +4309,7 @@
         <x:v>Chief Procurement Officer / Vendor and Contract Optimization data steward</x:v>
       </x:c>
       <x:c r="O76" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Vendor Contract Optimization Dashboard Inventory (record 71) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for data assets integrations.</x:v>
       </x:c>
       <x:c r="P76" t="str">
         <x:v>High</x:v>
@@ -4359,7 +4359,7 @@
         <x:v>Chief Procurement Officer / Vendor and Contract Optimization data steward</x:v>
       </x:c>
       <x:c r="O77" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm Vendor Contract Optimization Data Quality Rules (record 72) current-vs-target status, module boundary, volume baseline, and relationship links before this data assets integrations record is used downstream.</x:v>
       </x:c>
       <x:c r="P77" t="str">
         <x:v>High</x:v>
@@ -4409,7 +4409,7 @@
         <x:v>CTO / Infrastructure and CMDB data steward</x:v>
       </x:c>
       <x:c r="O78" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Attach client evidence for Infrastructure CMDB Operational Dataset (record 73), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P78" t="str">
         <x:v>Medium</x:v>
@@ -4459,7 +4459,7 @@
         <x:v>CTO / Infrastructure and CMDB data steward</x:v>
       </x:c>
       <x:c r="O79" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Reconcile Infrastructure CMDB Analytics Mart (record 74) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P79" t="str">
         <x:v>High</x:v>
@@ -4509,7 +4509,7 @@
         <x:v>CTO / Infrastructure and CMDB data steward</x:v>
       </x:c>
       <x:c r="O80" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Infrastructure CMDB Dashboard Inventory (record 75) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P80" t="str">
         <x:v>High</x:v>
@@ -4559,7 +4559,7 @@
         <x:v>CTO / Infrastructure and CMDB data steward</x:v>
       </x:c>
       <x:c r="O81" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Infrastructure CMDB Data Quality Rules (record 76) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for data assets integrations.</x:v>
       </x:c>
       <x:c r="P81" t="str">
         <x:v>High</x:v>
@@ -4609,7 +4609,7 @@
         <x:v>VP IT Operations / Incident Problem Change Operations data steward</x:v>
       </x:c>
       <x:c r="O82" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm Incident Problem Change Operations Operational Dataset (record 77) current-vs-target status, module boundary, volume baseline, and relationship links before this data assets integrations record is used downstream.</x:v>
       </x:c>
       <x:c r="P82" t="str">
         <x:v>Medium</x:v>
@@ -4659,7 +4659,7 @@
         <x:v>VP IT Operations / Incident Problem Change Operations data steward</x:v>
       </x:c>
       <x:c r="O83" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Attach client evidence for Incident Problem Change Operations Analytics Mart (record 78), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P83" t="str">
         <x:v>High</x:v>
@@ -4709,7 +4709,7 @@
         <x:v>VP IT Operations / Incident Problem Change Operations data steward</x:v>
       </x:c>
       <x:c r="O84" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Reconcile Incident Problem Change Operations Dashboard Inventory (record 79) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P84" t="str">
         <x:v>High</x:v>
@@ -4759,7 +4759,7 @@
         <x:v>VP IT Operations / Incident Problem Change Operations data steward</x:v>
       </x:c>
       <x:c r="O85" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Incident Problem Change Operations Data Quality Rules (record 80) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P85" t="str">
         <x:v>High</x:v>
@@ -4786,7 +4786,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf5dfcdef37d740c2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a95715527fd4aac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4861,7 +4861,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38d126e17cc14b48"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9161b265af894ebd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5055,7 +5055,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R106bf5bb9ce846f5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R999e0066cb3a4006"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5133,7 +5133,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfaa3d615cf684518"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92ac381f6fe94aef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5243,7 +5243,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7fa71786136b47ac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb94e77561cae4aed"/>
   </x:tableParts>
 </x:worksheet>
 </file>